--- a/n8n/shesterenka-leads-template.xlsx
+++ b/n8n/shesterenka-leads-template.xlsx
@@ -469,15 +469,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" style="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -498,31 +500,41 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Что случилось</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Запись</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Время</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:F1000">
+  <conditionalFormatting sqref="A2:H1000">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$F2="Новая"</formula>
+      <formula>$H2="Новая"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$F2="Отказ"</formula>
+      <formula>$H2="Отказ"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Статус" error="Выберите статус из списка" type="list">
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Статус" error="Выберите статус из списка" type="list">
       <formula1>"Новая,Перезвонили,Записан,Отказ"</formula1>
     </dataValidation>
   </dataValidations>
@@ -536,15 +548,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="70" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -605,81 +619,125 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Время</t>
+          <t>Услуга</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Время приёма заявки сервером n8n, по Москве.</t>
+          <t>Услуга, выбранная в форме. Пусто — клиенту нужна консультация.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Запись</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Желаемые день и время визита. Пусто — клиент не выбрал. Запись предварительная: подтвердите время по телефону.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>Время</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Время приёма заявки сервером n8n, по Москве.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
           <t>Пример строки (так её запишет n8n)</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Имя</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Марка</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Услуга</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Что случилось</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Запись</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Время</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="H12" s="6" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Иван</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>+79161234567</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Kia Rio 2018</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Ходовая часть</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>Стучит спереди справа на кочках</t>
         </is>
       </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>09.10.2026, 14:30:47</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>21.10.2026 10:00</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>19.10.2026, 14:30:47</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Новая</t>
         </is>

--- a/n8n/shesterenka-leads-template.xlsx
+++ b/n8n/shesterenka-leads-template.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -480,6 +480,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -523,9 +524,14 @@
           <t>Статус</t>
         </is>
       </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:H1000">
+  <conditionalFormatting sqref="A2:I1000">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$H2="Новая"</formula>
     </cfRule>
@@ -548,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -559,6 +565,7 @@
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -576,7 +583,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Заявка с сайта → вебхук n8n (n8n/shesterenka-leads.json) → новая строка на листе «Заявки».</t>
+          <t>Заявка с сайта или из Telegram-бота → n8n (n8n/shesterenka-leads.json) → новая строка на листе «Заявки».</t>
         </is>
       </c>
     </row>
@@ -652,6 +659,18 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Откуда заявка: telegram — из бота; с сайта — метка utm_source из ссылки (например, yandex), без метки — web.</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
@@ -700,6 +719,11 @@
           <t>Статус</t>
         </is>
       </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -740,6 +764,11 @@
       <c r="H13" s="7" t="inlineStr">
         <is>
           <t>Новая</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
